--- a/data/raw/individual/ID 009/continuous/mHLEA_excel/TUM_S009_mHLEA_excel_20250716.xlsx
+++ b/data/raw/individual/ID 009/continuous/mHLEA_excel/TUM_S009_mHLEA_excel_20250716.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarina/LRZ Sync+Share/Light Logger Study Data/raw/individual/ID 009/continuous/mHLEA_excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/MeLiDos/WP2.2.5_Data_Analysis/HildenEtAl_Dataset_2025/data/raw/individual/ID 009/continuous/mHLEA_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAFA846-1B86-8944-B308-69D39A159315}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4978A0F8-ED34-BC4D-BA5B-6F79C575C880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="19180" windowHeight="10780" xr2:uid="{B80439AF-1263-4DF6-B1CE-F20A60096DC5}"/>
+    <workbookView xWindow="1160" yWindow="780" windowWidth="19180" windowHeight="10780" xr2:uid="{B80439AF-1263-4DF6-B1CE-F20A60096DC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
     <t>L+I+E</t>
   </si>
   <si>
-    <t>8: Café indoors</t>
+    <t>Café indoors</t>
   </si>
 </sst>
 </file>
@@ -1970,7 +1970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <f t="shared" si="1"/>
         <v>45493.291666666359</v>
@@ -1982,7 +1982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <f t="shared" si="1"/>
         <v>45493.333333333023</v>
@@ -1994,7 +1994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <f t="shared" si="1"/>
         <v>45493.374999999687</v>
@@ -2006,7 +2006,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <f t="shared" ref="A132:A169" si="2">A131 + TIME(1, 0, 0)</f>
         <v>45493.416666666351</v>
@@ -2018,7 +2018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <f t="shared" si="2"/>
         <v>45493.458333333016</v>
@@ -2030,7 +2030,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <f t="shared" si="2"/>
         <v>45493.49999999968</v>
@@ -2042,7 +2042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <f t="shared" si="2"/>
         <v>45493.541666666344</v>
@@ -2054,7 +2054,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <f t="shared" si="2"/>
         <v>45493.583333333008</v>
@@ -2066,7 +2066,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <f t="shared" si="2"/>
         <v>45493.624999999673</v>
@@ -2078,7 +2078,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <f t="shared" si="2"/>
         <v>45493.666666666337</v>
@@ -2090,7 +2090,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <f t="shared" si="2"/>
         <v>45493.708333333001</v>
@@ -2098,11 +2098,14 @@
       <c r="B139" t="s">
         <v>6</v>
       </c>
-      <c r="C139" t="s">
+      <c r="C139">
+        <v>8</v>
+      </c>
+      <c r="D139" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <f t="shared" si="2"/>
         <v>45493.749999999665</v>
@@ -2110,11 +2113,14 @@
       <c r="B140" t="s">
         <v>6</v>
       </c>
-      <c r="C140" t="s">
+      <c r="C140">
+        <v>8</v>
+      </c>
+      <c r="D140" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <f t="shared" si="2"/>
         <v>45493.79166666633</v>
@@ -2126,7 +2132,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <f t="shared" si="2"/>
         <v>45493.833333332994</v>
@@ -2138,7 +2144,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <f t="shared" si="2"/>
         <v>45493.874999999658</v>
@@ -2150,7 +2156,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <f t="shared" si="2"/>
         <v>45493.916666666322</v>
